--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\82103\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{926456C7-2FBA-4B91-8E31-C54AEF9E2B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAA01EF-BE48-4B4A-B823-EDA82FF7A6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BBBA90A8-123E-467D-BE03-46C93887FB5D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="구성요소 및 구조도" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -505,12 +504,18 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -543,20 +548,23 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -575,6 +583,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>504825</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>515213</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>124777</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{811D4855-B233-6B27-74CD-00AD31BFE655}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5191125" y="1057275"/>
+          <a:ext cx="6182588" cy="6820852"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -902,791 +959,786 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="4" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="4" t="s">
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4" t="s">
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="4"/>
+      <c r="B6" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="4"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4" t="s">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="2" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4" t="s">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4" t="s">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="4" t="s">
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4" t="s">
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4" t="s">
+      <c r="A23" s="4"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4" t="s">
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4" t="s">
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4" t="s">
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4" t="s">
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3" t="s">
+      <c r="A28" s="4"/>
+      <c r="B28" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="2" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4" t="s">
+      <c r="A29" s="4"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4" t="s">
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="2" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4" t="s">
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4" t="s">
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4" t="s">
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4" t="s">
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4" t="s">
+      <c r="A36" s="4"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="2" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4" t="s">
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4" t="s">
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="2" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4" t="s">
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4" t="s">
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4" t="s">
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4" t="s">
+      <c r="A42" s="4"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="3" t="s">
+      <c r="A43" s="4"/>
+      <c r="B43" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4" t="s">
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="2" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="4" t="s">
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="3" t="s">
+      <c r="A46" s="4"/>
+      <c r="B46" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="4" t="s">
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="4" t="s">
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4" t="s">
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="4" t="s">
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="4" t="s">
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="4" t="s">
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="2" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="4" t="s">
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="4" t="s">
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="4" t="s">
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="4" t="s">
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="4" t="s">
+      <c r="A58" s="4"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="2" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="4" t="s">
+      <c r="A59" s="4"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="4" t="s">
+      <c r="A60" s="4"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="2" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-      <c r="B61" s="3" t="s">
+      <c r="A61" s="4"/>
+      <c r="B61" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2"/>
-      <c r="B62" s="3"/>
-      <c r="C62" s="4" t="s">
+      <c r="A62" s="4"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="4" t="s">
+      <c r="A63" s="4"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="4" t="s">
+      <c r="A64" s="4"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="2" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2"/>
-      <c r="B65" s="3" t="s">
+      <c r="A65" s="4"/>
+      <c r="B65" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="3"/>
-      <c r="C66" s="4" t="s">
+      <c r="A66" s="4"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="2" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="4" t="s">
+      <c r="A67" s="4"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="4" t="s">
+      <c r="A68" s="4"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="2" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="4" t="s">
+      <c r="A70" s="4"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="4" t="s">
+      <c r="A71" s="4"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="3" t="s">
+      <c r="A72" s="4"/>
+      <c r="B72" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="2" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="4" t="s">
+      <c r="A73" s="4"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="4" t="s">
+      <c r="A74" s="4"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2"/>
-      <c r="B75" s="3" t="s">
+      <c r="A75" s="4"/>
+      <c r="B75" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="4" t="s">
+      <c r="A76" s="4"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="4" t="s">
+      <c r="A77" s="4"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2"/>
-      <c r="B78" s="3" t="s">
+      <c r="A78" s="4"/>
+      <c r="B78" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="C78" s="4" t="s">
+      <c r="C78" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="4" t="s">
+      <c r="A79" s="4"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="4" t="s">
+      <c r="A80" s="4"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="2" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C81" s="4" t="s">
+      <c r="C81" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="4" t="s">
+      <c r="A82" s="4"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="2" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="4" t="s">
+      <c r="A83" s="4"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="4" t="s">
+      <c r="A84" s="4"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="2" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="4" t="s">
+      <c r="A85" s="4"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="4" t="s">
+      <c r="A86" s="4"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="2" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="4" t="s">
+      <c r="A87" s="4"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="4" t="s">
+      <c r="A88" s="4"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="2" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="4" t="s">
+      <c r="A89" s="4"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2"/>
-      <c r="B90" s="3" t="s">
+      <c r="A90" s="4"/>
+      <c r="B90" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="C90" s="4" t="s">
+      <c r="C90" s="2" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="4" t="s">
+      <c r="A91" s="4"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="4" t="s">
+      <c r="A92" s="4"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="2" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A93" s="2"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="4" t="s">
+      <c r="A93" s="4"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="4" t="s">
+      <c r="A94" s="4"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="2" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A95" s="2"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="4" t="s">
+      <c r="A95" s="4"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A96" s="2"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="4" t="s">
+      <c r="A96" s="4"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="2" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A97" s="2"/>
-      <c r="B97" s="3" t="s">
+      <c r="A97" s="4"/>
+      <c r="B97" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C97" s="4" t="s">
+      <c r="C97" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A98" s="2"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="4" t="s">
+      <c r="A98" s="4"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="2" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="2"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="4" t="s">
+      <c r="A99" s="4"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B100" s="3" t="s">
+      <c r="B100" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C100" s="4" t="s">
+      <c r="C100" s="2" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A101" s="2"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="4" t="s">
+      <c r="A101" s="4"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A102" s="2"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="4" t="s">
+      <c r="A102" s="4"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="2" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A103" s="2"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="4" t="s">
+      <c r="A103" s="4"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="2" t="s">
         <v>101</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="B28:B33"/>
-    <mergeCell ref="B81:B89"/>
-    <mergeCell ref="B90:B96"/>
-    <mergeCell ref="B97:B99"/>
     <mergeCell ref="A34:A55"/>
     <mergeCell ref="B34:B42"/>
     <mergeCell ref="B43:B45"/>
@@ -1697,6 +1749,8 @@
     <mergeCell ref="B12:B15"/>
     <mergeCell ref="A16:A33"/>
     <mergeCell ref="B16:B20"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="B28:B33"/>
     <mergeCell ref="A100:A103"/>
     <mergeCell ref="B100:B103"/>
     <mergeCell ref="A56:A68"/>
@@ -1709,21 +1763,12 @@
     <mergeCell ref="B72:B74"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B81:B89"/>
+    <mergeCell ref="B90:B96"/>
+    <mergeCell ref="B97:B99"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540833B4-74DC-4893-A4AD-93647C53E0AD}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="2" width="22.5" customWidth="1"/>
-  </cols>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>